--- a/us-dcf/tests/fixtures/AAPL_DCF.xlsx
+++ b/us-dcf/tests/fixtures/AAPL_DCF.xlsx
@@ -9467,23 +9467,23 @@
         <v/>
       </c>
       <c r="B90" s="58">
-        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A90,(B$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(B$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/($B$35*(1-$B$34)/$B$42)))/($A90-B$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A90,(B$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(B$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A90-B$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="C90" s="58">
-        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A90,(C$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(C$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/($B$35*(1-$B$34)/$B$42)))/($A90-C$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A90,(C$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(C$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A90-C$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="D90" s="58">
-        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A90,(D$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(D$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/($B$35*(1-$B$34)/$B$42)))/($A90-D$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A90,(D$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(D$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A90-D$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="E90" s="58">
-        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A90,(E$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(E$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/($B$35*(1-$B$34)/$B$42)))/($A90-E$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A90,(E$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(E$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A90-E$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="F90" s="58">
-        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A90,(F$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(F$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/($B$35*(1-$B$34)/$B$42)))/($A90-F$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A90)^(1-0.5*$B$16)+$C$28/(1+$A90)^(2-0.5*$B$16)+$D$28/(1+$A90)^(3-0.5*$B$16)+$E$28/(1+$A90)^(4-0.5*$B$16)+$F$28/(1+$A90)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A90,(F$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(F$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A90,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/IF('1_Assumptions'!$B$123=2,$A90+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A90-F$89)))/(1+$A90)^(5-0.5*$B$16))*(1+$A90)^$B$58-$B$28*$B$58*(1+$A90)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
     </row>
@@ -9493,23 +9493,23 @@
         <v/>
       </c>
       <c r="B91" s="58">
-        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A91,(B$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(B$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/($B$35*(1-$B$34)/$B$42)))/($A91-B$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A91,(B$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(B$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A91-B$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="C91" s="58">
-        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A91,(C$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(C$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/($B$35*(1-$B$34)/$B$42)))/($A91-C$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A91,(C$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(C$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A91-C$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="D91" s="58">
-        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A91,(D$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(D$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/($B$35*(1-$B$34)/$B$42)))/($A91-D$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A91,(D$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(D$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A91-D$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="E91" s="58">
-        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A91,(E$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(E$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/($B$35*(1-$B$34)/$B$42)))/($A91-E$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A91,(E$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(E$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A91-E$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="F91" s="58">
-        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A91,(F$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(F$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/($B$35*(1-$B$34)/$B$42)))/($A91-F$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A91)^(1-0.5*$B$16)+$C$28/(1+$A91)^(2-0.5*$B$16)+$D$28/(1+$A91)^(3-0.5*$B$16)+$E$28/(1+$A91)^(4-0.5*$B$16)+$F$28/(1+$A91)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A91,(F$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(F$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A91,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/IF('1_Assumptions'!$B$123=2,$A91+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A91-F$89)))/(1+$A91)^(5-0.5*$B$16))*(1+$A91)^$B$58-$B$28*$B$58*(1+$A91)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
     </row>
@@ -9519,23 +9519,23 @@
         <v/>
       </c>
       <c r="B92" s="58">
-        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A92,(B$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(B$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/($B$35*(1-$B$34)/$B$42)))/($A92-B$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A92,(B$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(B$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A92-B$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="C92" s="58">
-        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A92,(C$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(C$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/($B$35*(1-$B$34)/$B$42)))/($A92-C$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A92,(C$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(C$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A92-C$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="D92" s="58">
-        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A92,(D$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(D$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/($B$35*(1-$B$34)/$B$42)))/($A92-D$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A92,(D$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(D$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A92-D$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="E92" s="58">
-        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A92,(E$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(E$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/($B$35*(1-$B$34)/$B$42)))/($A92-E$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A92,(E$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(E$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A92-E$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="F92" s="58">
-        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A92,(F$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(F$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/($B$35*(1-$B$34)/$B$42)))/($A92-F$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A92)^(1-0.5*$B$16)+$C$28/(1+$A92)^(2-0.5*$B$16)+$D$28/(1+$A92)^(3-0.5*$B$16)+$E$28/(1+$A92)^(4-0.5*$B$16)+$F$28/(1+$A92)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A92,(F$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(F$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A92,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/IF('1_Assumptions'!$B$123=2,$A92+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A92-F$89)))/(1+$A92)^(5-0.5*$B$16))*(1+$A92)^$B$58-$B$28*$B$58*(1+$A92)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
     </row>
@@ -9545,23 +9545,23 @@
         <v/>
       </c>
       <c r="B93" s="58">
-        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A93,(B$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(B$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/($B$35*(1-$B$34)/$B$42)))/($A93-B$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A93,(B$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(B$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A93-B$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="C93" s="58">
-        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A93,(C$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(C$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/($B$35*(1-$B$34)/$B$42)))/($A93-C$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A93,(C$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(C$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A93-C$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="D93" s="58">
-        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A93,(D$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(D$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/($B$35*(1-$B$34)/$B$42)))/($A93-D$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A93,(D$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(D$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A93-D$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="E93" s="58">
-        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A93,(E$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(E$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/($B$35*(1-$B$34)/$B$42)))/($A93-E$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A93,(E$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(E$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A93-E$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="F93" s="58">
-        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A93,(F$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(F$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/($B$35*(1-$B$34)/$B$42)))/($A93-F$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A93)^(1-0.5*$B$16)+$C$28/(1+$A93)^(2-0.5*$B$16)+$D$28/(1+$A93)^(3-0.5*$B$16)+$E$28/(1+$A93)^(4-0.5*$B$16)+$F$28/(1+$A93)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A93,(F$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(F$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A93,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/IF('1_Assumptions'!$B$123=2,$A93+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A93-F$89)))/(1+$A93)^(5-0.5*$B$16))*(1+$A93)^$B$58-$B$28*$B$58*(1+$A93)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
     </row>
@@ -9571,23 +9571,23 @@
         <v/>
       </c>
       <c r="B94" s="58">
-        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A94,(B$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(B$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/($B$35*(1-$B$34)/$B$42)))/($A94-B$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A94,(B$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(B$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+B$89)*(1-$B$34)*(1-(B$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A94-B$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="C94" s="58">
-        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A94,(C$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(C$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/($B$35*(1-$B$34)/$B$42)))/($A94-C$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A94,(C$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(C$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+C$89)*(1-$B$34)*(1-(C$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A94-C$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="D94" s="58">
-        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A94,(D$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(D$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/($B$35*(1-$B$34)/$B$42)))/($A94-D$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A94,(D$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(D$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+D$89)*(1-$B$34)*(1-(D$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A94-D$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="E94" s="58">
-        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A94,(E$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(E$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/($B$35*(1-$B$34)/$B$42)))/($A94-E$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A94,(E$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(E$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+E$89)*(1-$B$34)*(1-(E$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A94-E$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
       <c r="F94" s="58">
-        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,($B$35*(1-$B$34)/$B$42)&lt;=$A94,(F$89/($B$35*(1-$B$34)/$B$42))&gt;=1,(F$89/($B$35*(1-$B$34)/$B$42))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/($B$35*(1-$B$34)/$B$42)))/($A94-F$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
+        <f>(((($B$28/(1+$A94)^(1-0.5*$B$16)+$C$28/(1+$A94)^(2-0.5*$B$16)+$D$28/(1+$A94)^(3-0.5*$B$16)+$E$28/(1+$A94)^(4-0.5*$B$16)+$F$28/(1+$A94)^(5-0.5*$B$16))+(IF(OR($B$42&lt;=0,IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))&lt;=$A94,(F$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&gt;=1,(F$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42)))&lt;0),($B$35*(1-$B$34))/$A94,$B$35*(1+F$89)*(1-$B$34)*(1-(F$89/IF('1_Assumptions'!$B$123=2,$A94+'1_Assumptions'!$B$124,($B$35*(1-$B$34)/$B$42))))/($A94-F$89)))/(1+$A94)^(5-0.5*$B$16))*(1+$A94)^$B$58-$B$28*$B$58*(1+$A94)^($B$58/2)-$B$60+$B$61+$B$62)*(1-IF($B$64=1,0,$B$65))-IF($B$64=1,'1_Assumptions'!$B$95,0))/$B$68</f>
         <v/>
       </c>
     </row>
